--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G35" s="19" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G36" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G38" s="19" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G40" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G46" s="19" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G48" s="19" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G50" s="19" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G52" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G54" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -3332,7 +3332,7 @@
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G55" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G56" s="19" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G58" s="19" t="inlineStr">

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH88"/>
+  <dimension ref="A1:AH96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4813,6 +4813,100 @@
       <c r="A88" s="4" t="inlineStr">
         <is>
           <t>Perbarui kolom Status ke Backlog / In Progress / Done / On Hold / Won't Do / Potential Delay. Kolom Jam Tersisa menunjukkan sisa beban sebenarnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CATATAN KECEPATAN AKTUAL (diisi 4 September 2026, berbasis timestamp commit git)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Waktu nyata untuk task 7 s/d 30 (fondasi s/d F-08 + grafik)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>4 jam 41 menit</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Diukur dari commit pertama (16:55) sampai commit terakhir sesi (21:36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estimasi roadmap untuk task yang sama</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>227 jam</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>68% dari total 336 jam roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Rasio kompresi</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>~48x</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Karena bantuan AI pair-programming, bukan indikasi estimasi awal salah</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Catatan penting</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Estimasi 12,5 jam/hari x 27 hari REALISTIS untuk solo coding manual tanpa AI. Kompresi terjadi karena mode kerja berbeda (AI-assisted), bukan karena estimasi awal keliru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Yang TIDAK ikut terkompresi</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Waktu tunggu API eksternal (mis. gangguan Gemini 503 memakan puluhan menit), video/narasi (kerja kreatif manusia), review manual/QA akhir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Implikasi</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sisa task dev (tooltip, bug fixing, polish) realistis selesai dalam hitungan jam-hari, bukan minggu. Sisa waktu (26 hari ke deadline 30 Sep) dialokasikan ke: testing lebih dalam, video/narasi matang, buffer risiko.</t>
         </is>
       </c>
     </row>

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -19,7 +19,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -46,6 +46,9 @@
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -181,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,6 +265,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH96"/>
+  <dimension ref="A1:AH101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3852,7 +3856,7 @@
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G64" s="19" t="inlineStr">
@@ -4907,6 +4911,83 @@
       <c r="B96" t="inlineStr">
         <is>
           <t>Sisa task dev (tooltip, bug fixing, polish) realistis selesai dalam hitungan jam-hari, bukan minggu. Sisa waktu (26 hari ke deadline 30 Sep) dialokasikan ke: testing lebih dalam, video/narasi matang, buffer risiko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="32" t="inlineStr">
+        <is>
+          <t>CATATAN PROGRES UI (5 September 2026)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Dashboard (Ringkasan Pasar)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Urutan dokumen dibalik agar analisis turunan tampil lebih dulu; screener multi-faktor; strip deteksi anomali lintas emiten teramai; asisten AI mengambang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Halaman detail emiten</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dibangun ulang mengikuti mockup: kartu identitas, grafik dengan toolbar berfungsi penuh, konteks sub-sektor, tabel multiples lima tahun, statistik harga, kabar emiten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Halaman Berita dan Detail Berita</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Masih memakai tata letak lama dan kini paling tertinggal dibanding dua halaman lain. Prioritas berikutnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Item menggantung</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tiga menu navigasi tanpa halaman; tombol Simpan Watchlist dan Buat Price Alert masih nonaktif; verifikasi independen skor komposit belum dijalankan.</t>
         </is>
       </c>
     </row>

--- a/docs/Roadmap Solo Sectors Hackathon.xlsx
+++ b/docs/Roadmap Solo Sectors Hackathon.xlsx
@@ -559,6 +559,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -601,6 +602,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="H7" s="14" t="inlineStr">
         <is>
@@ -3576,7 +3578,7 @@
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G59" s="19" t="inlineStr">
@@ -4740,6 +4742,7 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
@@ -4813,6 +4816,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
@@ -4820,6 +4824,7 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -4920,8 +4925,6 @@
           <t>CATATAN PROGRES UI (5 September 2026)</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4987,7 +4990,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tiga menu navigasi tanpa halaman; tombol Simpan Watchlist dan Buat Price Alert masih nonaktif; verifikasi independen skor komposit belum dijalankan.</t>
+          <t>Tidak ada lagi item menggantung. SELESAI 5-6 Sep: verifikasi independen skor komposit; penutupan tiga kebocoran kredit (dedup in-flight, TTL cache, rentang tanggal); halaman /berita; route /berita/:id; penghapusan seluruh menu dan tombol mati; tooltip glosarium (task 31); koreksi label DER; perbaikan bug ticker ganda; pembesaran navbar dan penambahan navigasi mobile. Berikutnya: deliverable non-kode (video teaser 1 menit, video juri 3 menit, problem statement, post media sosial) dan push dua commit yang masih tertinggal.</t>
         </is>
       </c>
     </row>
